--- a/data/trans_orig/IP1003-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP1003-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>3291</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11425</t>
+          <t>11199</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1636</t>
+          <t>1981</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8940</t>
+          <t>9050</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6163</t>
+          <t>6389</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>16503</t>
+          <t>17552</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,88%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>79442</t>
+          <t>79668</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>87636</t>
+          <t>87576</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>87,43%</t>
+          <t>87,68%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,44%</t>
+          <t>96,38%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>77905</t>
+          <t>77795</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>85209</t>
+          <t>84864</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>89,71%</t>
+          <t>89,58%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>97,72%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>161209</t>
+          <t>160160</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>171549</t>
+          <t>171323</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,71%</t>
+          <t>90,12%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,53%</t>
+          <t>96,4%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16501</t>
+          <t>16890</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>31725</t>
+          <t>32266</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>27311</t>
+          <t>27083</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>45169</t>
+          <t>45780</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>47246</t>
+          <t>47244</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>71150</t>
+          <t>70100</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>7,85%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>384362</t>
+          <t>383821</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>399586</t>
+          <t>399197</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,38%</t>
+          <t>92,25%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>95,94%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>431822</t>
+          <t>431211</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>449680</t>
+          <t>449908</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,53%</t>
+          <t>90,4%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,27%</t>
+          <t>94,32%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>821928</t>
+          <t>822978</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>845832</t>
+          <t>845834</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,03%</t>
+          <t>92,15%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6062</t>
+          <t>6118</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16200</t>
+          <t>16708</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6218</t>
+          <t>6522</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>16468</t>
+          <t>17066</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>14806</t>
+          <t>14691</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>29165</t>
+          <t>30071</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>9,05%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>157866</t>
+          <t>157358</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>168004</t>
+          <t>167948</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,69%</t>
+          <t>90,4%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>96,49%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>141670</t>
+          <t>141072</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>151920</t>
+          <t>151616</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,59%</t>
+          <t>89,21%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>95,88%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>303040</t>
+          <t>302134</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>317399</t>
+          <t>317514</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,22%</t>
+          <t>90,95%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>95,58%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>32109</t>
+          <t>30846</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>51320</t>
+          <t>51436</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>40965</t>
+          <t>38946</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>61839</t>
+          <t>62203</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>76146</t>
+          <t>76456</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>103890</t>
+          <t>107054</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,63%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>629701</t>
+          <t>629585</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>648912</t>
+          <t>650175</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,46%</t>
+          <t>92,45%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,29%</t>
+          <t>95,47%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>660135</t>
+          <t>659771</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>681009</t>
+          <t>683028</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,43%</t>
+          <t>91,38%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,33%</t>
+          <t>94,61%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1299105</t>
+          <t>1295941</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1326849</t>
+          <t>1326539</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,6%</t>
+          <t>92,37%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,57%</t>
+          <t>94,55%</t>
         </is>
       </c>
     </row>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1481</t>
+          <t>1496</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8918</t>
+          <t>8879</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3075</t>
+          <t>2851</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11496</t>
+          <t>11243</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,47 +2386,47 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
+          <t>3,41%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>13,46%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>10708</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>6452</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>16909</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>6,1%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
           <t>3,68%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>13,76%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>10708</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>6519</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>17576</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>6,1%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>3,72%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>9,64%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>82971</t>
+          <t>83010</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>90408</t>
+          <t>90393</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,29%</t>
+          <t>90,34%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,37%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>72041</t>
+          <t>72294</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>80462</t>
+          <t>80686</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,47 +2499,47 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>86,24%</t>
+          <t>86,54%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
+          <t>96,59%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>235</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>164717</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>158516</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>168973</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>93,9%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>90,36%</t>
+        </is>
+      </c>
+      <c r="W5" s="2" t="inlineStr">
+        <is>
           <t>96,32%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>235</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>164717</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>157849</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>168906</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>93,9%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>89,98%</t>
-        </is>
-      </c>
-      <c r="W5" s="2" t="inlineStr">
-        <is>
-          <t>96,28%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14162</t>
+          <t>14414</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>30087</t>
+          <t>29938</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>21335</t>
+          <t>22901</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>39595</t>
+          <t>40065</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>40439</t>
+          <t>41754</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>63987</t>
+          <t>64785</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,88%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>418985</t>
+          <t>419134</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>434910</t>
+          <t>434658</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,3%</t>
+          <t>93,33%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>96,79%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>452809</t>
+          <t>452339</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>471069</t>
+          <t>469503</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,96%</t>
+          <t>91,86%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>95,35%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>877489</t>
+          <t>876691</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>901037</t>
+          <t>899722</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,2%</t>
+          <t>93,12%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,7%</t>
+          <t>95,57%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3568</t>
+          <t>3832</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12449</t>
+          <t>12578</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5189</t>
+          <t>4940</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>15134</t>
+          <t>14999</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>9903</t>
+          <t>10813</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>23526</t>
+          <t>23173</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>6,88%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>152891</t>
+          <t>152762</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>161772</t>
+          <t>161508</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,47%</t>
+          <t>92,39%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,68%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>156427</t>
+          <t>156562</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>166372</t>
+          <t>166621</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,18%</t>
+          <t>91,26%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>97,12%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>313375</t>
+          <t>313728</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>326998</t>
+          <t>326088</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,02%</t>
+          <t>93,12%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>96,79%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>24255</t>
+          <t>24901</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>43089</t>
+          <t>44335</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>35934</t>
+          <t>35238</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>57765</t>
+          <t>57423</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>65690</t>
+          <t>65284</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>95026</t>
+          <t>93745</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,45%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>663212</t>
+          <t>661966</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>682046</t>
+          <t>681400</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,9%</t>
+          <t>93,72%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>96,47%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>689736</t>
+          <t>690078</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>711567</t>
+          <t>712263</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,27%</t>
+          <t>92,32%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,19%</t>
+          <t>95,29%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1358776</t>
+          <t>1360057</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1388112</t>
+          <t>1388518</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,46%</t>
+          <t>93,55%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,48%</t>
+          <t>95,51%</t>
         </is>
       </c>
     </row>
@@ -3944,7 +3944,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2742</t>
+          <t>2740</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3959,7 +3959,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2821</t>
+          <t>2692</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10771</t>
+          <t>10444</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,7%</t>
+          <t>15,22%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3408</t>
+          <t>2842</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12055</t>
+          <t>10848</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>8,48%</t>
         </is>
       </c>
     </row>
@@ -4052,7 +4052,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>56636</t>
+          <t>56638</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -4067,7 +4067,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>95,39%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>57843</t>
+          <t>58170</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>65793</t>
+          <t>65922</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>84,3%</t>
+          <t>84,78%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,89%</t>
+          <t>96,08%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>115938</t>
+          <t>117145</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>124585</t>
+          <t>125151</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,58%</t>
+          <t>91,52%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>97,78%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16695</t>
+          <t>16590</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>31440</t>
+          <t>31488</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>18986</t>
+          <t>18618</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>36466</t>
+          <t>36711</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>39498</t>
+          <t>38703</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>63589</t>
+          <t>62063</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,46%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>440850</t>
+          <t>440802</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>455595</t>
+          <t>455700</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,34%</t>
+          <t>93,33%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,49%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>452269</t>
+          <t>452024</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>469749</t>
+          <t>470117</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,54%</t>
+          <t>92,49%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>96,19%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>897436</t>
+          <t>898962</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>921527</t>
+          <t>922322</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,38%</t>
+          <t>93,54%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,89%</t>
+          <t>95,97%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4372</t>
+          <t>4156</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>14729</t>
+          <t>14615</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2573</t>
+          <t>2296</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10697</t>
+          <t>10890</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8514</t>
+          <t>8430</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>21572</t>
+          <t>21275</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>5,91%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>157974</t>
+          <t>158088</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>168331</t>
+          <t>168547</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,47%</t>
+          <t>91,54%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,59%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>176798</t>
+          <t>176605</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>184922</t>
+          <t>185199</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,29%</t>
+          <t>94,19%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,78%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>338625</t>
+          <t>338922</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>351683</t>
+          <t>351767</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,01%</t>
+          <t>94,09%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>97,66%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>23846</t>
+          <t>23611</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>43540</t>
+          <t>41695</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>29223</t>
+          <t>29652</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>50166</t>
+          <t>50237</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>58482</t>
+          <t>57546</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>86083</t>
+          <t>85532</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,9%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>660831</t>
+          <t>662676</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>680525</t>
+          <t>680760</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,82%</t>
+          <t>94,08%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>96,65%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>694678</t>
+          <t>694607</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>715621</t>
+          <t>715192</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5136,7 +5136,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>96,02%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1363132</t>
+          <t>1363683</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1390733</t>
+          <t>1391669</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,06%</t>
+          <t>94,1%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>96,03%</t>
         </is>
       </c>
     </row>
@@ -5542,12 +5542,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>617</t>
+          <t>625</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6138</t>
+          <t>6630</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3301</t>
+          <t>3194</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13508</t>
+          <t>13822</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>22,29%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4676</t>
+          <t>4346</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>16931</t>
+          <t>17940</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5627,12 +5627,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>15,38%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>48540</t>
+          <t>48048</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>54061</t>
+          <t>54053</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>88,77%</t>
+          <t>87,87%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,86%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>48496</t>
+          <t>48182</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>58703</t>
+          <t>58810</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>78,21%</t>
+          <t>77,71%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,68%</t>
+          <t>94,85%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>99751</t>
+          <t>98742</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>112006</t>
+          <t>112336</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>85,49%</t>
+          <t>84,62%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,99%</t>
+          <t>96,28%</t>
         </is>
       </c>
     </row>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18664</t>
+          <t>18336</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>36721</t>
+          <t>36465</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>30038</t>
+          <t>29414</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>54444</t>
+          <t>53353</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>53560</t>
+          <t>53745</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>82590</t>
+          <t>86320</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5970,12 +5970,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,86%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>422348</t>
+          <t>422604</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>440405</t>
+          <t>440733</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,0%</t>
+          <t>92,06%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>96,01%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>460381</t>
+          <t>461472</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>484787</t>
+          <t>485411</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,42%</t>
+          <t>89,64%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,17%</t>
+          <t>94,29%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>891304</t>
+          <t>887574</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>920334</t>
+          <t>920149</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,52%</t>
+          <t>91,14%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,5%</t>
+          <t>94,48%</t>
         </is>
       </c>
     </row>
@@ -6228,12 +6228,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4243</t>
+          <t>3775</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13811</t>
+          <t>12765</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8781</t>
+          <t>9175</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>23938</t>
+          <t>24403</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>13,31%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>15087</t>
+          <t>15420</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>32147</t>
+          <t>32828</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6313,12 +6313,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>9,89%</t>
         </is>
       </c>
     </row>
@@ -6341,12 +6341,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>134909</t>
+          <t>135955</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>144477</t>
+          <t>144945</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6356,12 +6356,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,71%</t>
+          <t>91,42%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>159411</t>
+          <t>158946</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>174568</t>
+          <t>174174</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6391,12 +6391,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>86,94%</t>
+          <t>86,69%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,21%</t>
+          <t>95,0%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>299922</t>
+          <t>299241</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>316982</t>
+          <t>316649</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6426,12 +6426,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,32%</t>
+          <t>90,11%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>95,36%</t>
         </is>
       </c>
     </row>
@@ -6571,12 +6571,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>26276</t>
+          <t>27402</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>47673</t>
+          <t>50210</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>49192</t>
+          <t>49293</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>80052</t>
+          <t>79927</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6641,7 +6641,7 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>82792</t>
+          <t>80718</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
@@ -6656,7 +6656,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -6684,12 +6684,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>614794</t>
+          <t>612257</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>636191</t>
+          <t>635065</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,8%</t>
+          <t>92,42%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>95,86%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>680125</t>
+          <t>680250</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>710985</t>
+          <t>710884</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,47%</t>
+          <t>89,49%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,53%</t>
+          <t>93,52%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6759,7 +6759,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1339853</t>
+          <t>1341927</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6774,7 +6774,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,18%</t>
+          <t>94,33%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP1003-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP1003-Estudios-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -723,74 +723,74 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>4367</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>8922</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>5,03%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>2,33%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>10,27%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>6383</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>3291</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>11199</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>3171</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>11195</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>7,02%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>3,62%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>3,49%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>12,32%</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>4367</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>1981</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>9050</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>5,03%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>2,28%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>10,42%</t>
-        </is>
-      </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>16</t>
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6389</t>
+          <t>6303</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>17552</t>
+          <t>16996</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>9,56%</t>
         </is>
       </c>
     </row>
@@ -836,72 +836,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>82478</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>77923</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>84825</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>94,97%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>89,73%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>97,67%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>126</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>84484</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>79668</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>87576</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>79672</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>87696</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>92,98%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>87,68%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>96,38%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>124</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>82478</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>77795</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>84864</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>94,97%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>89,58%</t>
-        </is>
-      </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>96,51%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>160160</t>
+          <t>160716</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>171323</t>
+          <t>171409</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,12%</t>
+          <t>90,44%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,4%</t>
+          <t>96,45%</t>
         </is>
       </c>
     </row>
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>86845</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>86845</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>86845</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>136</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>90867</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>90867</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>90867</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>86845</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>86845</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>86845</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1066,72 +1066,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>35222</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>26993</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>46355</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>7,38%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>5,66%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>9,72%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>35</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>23503</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>16890</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>32266</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>16935</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>31593</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>5,65%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>4,06%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>7,75%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>35222</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>27083</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>45780</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>7,38%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>47244</t>
+          <t>48092</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>70100</t>
+          <t>72783</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>8,15%</t>
         </is>
       </c>
     </row>
@@ -1179,72 +1179,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>665</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>441769</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>430636</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>449998</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>92,62%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>90,28%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>94,34%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>593</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>392584</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>383821</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>399197</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>384494</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>399152</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>94,35%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>92,25%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>95,94%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>665</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>441769</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>431211</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>449908</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>92,62%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,4%</t>
+          <t>92,41%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,32%</t>
+          <t>95,93%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>822978</t>
+          <t>820295</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>845834</t>
+          <t>844986</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,15%</t>
+          <t>91,85%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,71%</t>
+          <t>94,62%</t>
         </is>
       </c>
     </row>
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>719</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>476991</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>476991</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>476991</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>628</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>416087</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>416087</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>416087</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>719</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>476991</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>476991</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>476991</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1409,72 +1409,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>10377</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>5810</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>16948</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>6,56%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>3,67%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>10,72%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>10753</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>6118</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>16708</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>6451</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>16853</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>6,18%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>3,51%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>9,6%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>10377</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>6522</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>17066</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>6,56%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>14691</t>
+          <t>14712</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>30071</t>
+          <t>29431</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>8,86%</t>
         </is>
       </c>
     </row>
@@ -1522,72 +1522,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>221</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>147761</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>141190</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>152328</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>93,44%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>89,28%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>96,33%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>238</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>163313</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>157358</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>167948</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>157213</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>167615</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>93,82%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>90,4%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>96,49%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>221</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>147761</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>141072</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>151616</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>93,44%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,21%</t>
+          <t>90,32%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,88%</t>
+          <t>96,29%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>302134</t>
+          <t>302774</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>317514</t>
+          <t>317493</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,95%</t>
+          <t>91,14%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>95,57%</t>
         </is>
       </c>
     </row>
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>236</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>158138</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>158138</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>158138</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>254</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>174066</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>174066</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>174066</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>236</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>158138</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>158138</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>158138</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1752,72 +1752,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>49967</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>39270</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>61155</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>6,92%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>5,44%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>8,47%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>61</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>40639</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>30846</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>51436</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>31291</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>50830</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>5,97%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>4,53%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>7,55%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>49967</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>38946</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>62203</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>6,92%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>76456</t>
+          <t>76570</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>107054</t>
+          <t>106562</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,6%</t>
         </is>
       </c>
     </row>
@@ -1865,72 +1865,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>1010</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>672007</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>660819</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>682704</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>93,08%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>91,53%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>94,56%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>957</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>640382</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>629585</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>650175</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>630191</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>649730</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>94,03%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>92,45%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>95,47%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>1010</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>672007</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>659771</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>683028</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>93,08%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,38%</t>
+          <t>92,54%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,61%</t>
+          <t>95,41%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1295941</t>
+          <t>1296433</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1326539</t>
+          <t>1326425</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,37%</t>
+          <t>92,4%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,55%</t>
+          <t>94,54%</t>
         </is>
       </c>
     </row>
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>1085</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>721974</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>721974</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>721974</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>1018</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>681021</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>1085</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>721974</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>721974</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>721974</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2147,7 +2147,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2158,7 +2158,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2326,72 +2326,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>6315</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>3067</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>11051</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>7,56%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>3,67%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>13,23%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>4393</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>1496</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>8879</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>1999</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>8894</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>4,78%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>1,63%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>9,66%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>6315</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>2851</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>11243</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>7,56%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6452</t>
+          <t>6642</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>16909</t>
+          <t>17886</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>10,2%</t>
         </is>
       </c>
     </row>
@@ -2439,72 +2439,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>77222</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>72486</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>80470</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>92,44%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>86,77%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>96,33%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>127</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>87496</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>83010</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>90393</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>82995</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>89890</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>95,22%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>90,34%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>98,37%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>108</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>77222</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>72294</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>80686</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>92,44%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>86,54%</t>
+          <t>90,32%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,59%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>158516</t>
+          <t>157539</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>168973</t>
+          <t>168783</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,36%</t>
+          <t>89,8%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,32%</t>
+          <t>96,21%</t>
         </is>
       </c>
     </row>
@@ -2552,57 +2552,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>83537</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>83537</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>83537</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>133</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>91889</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>91889</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>91889</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>117</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>83537</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>83537</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>83537</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -2669,72 +2669,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>30193</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>22461</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>40699</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>6,13%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>4,56%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>8,27%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>21591</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>14414</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>29938</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>15044</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>30940</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>4,81%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>3,21%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>6,67%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>30193</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>22901</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>40065</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>6,13%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>41754</t>
+          <t>42075</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>64785</t>
+          <t>63829</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,78%</t>
         </is>
       </c>
     </row>
@@ -2782,72 +2782,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>662</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>462211</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>451705</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>469943</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>93,87%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>91,73%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>95,44%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>620</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>427481</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>419134</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>434658</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>418132</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>434028</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>95,19%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>93,33%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>96,79%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>662</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>462211</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>452339</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>469503</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>93,87%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,86%</t>
+          <t>93,11%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>96,65%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>876691</t>
+          <t>877647</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>899722</t>
+          <t>899401</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,12%</t>
+          <t>93,22%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,57%</t>
+          <t>95,53%</t>
         </is>
       </c>
     </row>
@@ -2895,57 +2895,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>705</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>492404</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>492404</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>492404</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>650</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>449072</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>449072</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>449072</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>705</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>492404</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>492404</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>492404</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3012,72 +3012,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>9160</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>5324</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>15907</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>5,34%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>3,1%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>9,27%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>7205</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>3832</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>12578</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>3636</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>13157</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>4,36%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>2,32%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>7,61%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>9160</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>4940</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>14999</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>5,34%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>10813</t>
+          <t>10663</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>23173</t>
+          <t>24287</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>7,21%</t>
         </is>
       </c>
     </row>
@@ -3125,72 +3125,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>162401</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>155654</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>166237</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>94,66%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>90,73%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>96,9%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>224</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>158135</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>152762</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>161508</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>152183</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>161704</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>95,64%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>92,39%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>97,68%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>230</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>162401</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>156562</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>166621</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>94,66%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,26%</t>
+          <t>92,04%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>313728</t>
+          <t>312614</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>326088</t>
+          <t>326238</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,12%</t>
+          <t>92,79%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>96,83%</t>
         </is>
       </c>
     </row>
@@ -3238,57 +3238,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>243</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>171561</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>171561</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>171561</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>234</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>165340</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>165340</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>165340</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>243</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>171561</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>171561</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>171561</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3355,72 +3355,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>45668</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>36105</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>59535</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>6,11%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>4,83%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>7,96%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>46</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>33189</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>24901</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>44335</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>24394</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>43668</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>4,7%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>3,53%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>6,28%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>45668</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>35238</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>57423</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>6,11%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>65284</t>
+          <t>65502</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>93745</t>
+          <t>94597</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,51%</t>
         </is>
       </c>
     </row>
@@ -3468,72 +3468,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>701833</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>687966</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>711396</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>93,89%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>92,04%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>95,17%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>971</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>673112</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>661966</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>681400</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>662633</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>681907</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>95,3%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>93,72%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>96,47%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>701833</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>690078</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>712263</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>93,89%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,32%</t>
+          <t>93,82%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,29%</t>
+          <t>96,55%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1360057</t>
+          <t>1359205</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1388518</t>
+          <t>1388300</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,55%</t>
+          <t>93,49%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,51%</t>
+          <t>95,49%</t>
         </is>
       </c>
     </row>
@@ -3581,57 +3581,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>1065</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>747501</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>747501</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>747501</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>1017</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>706301</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>706301</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>706301</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>1065</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>747501</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>747501</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>747501</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -3750,7 +3750,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3761,7 +3761,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -3929,72 +3929,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>5752</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2814</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>11804</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>8,38%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>4,1%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>17,2%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>664</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2740</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>3519</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>1,12%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>4,61%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>5752</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>2692</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>10444</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>8,38%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>3,92%</t>
-        </is>
-      </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2842</t>
+          <t>3072</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>10848</t>
+          <t>11674</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>9,12%</t>
         </is>
       </c>
     </row>
@@ -4042,74 +4042,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>62862</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>56810</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>65800</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>91,62%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>82,8%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>95,9%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>88</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>58714</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>56638</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>55859</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>59378</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>98,88%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>95,39%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>94,07%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>62862</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>58170</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>65922</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>91,62%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>84,78%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>96,08%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>179</t>
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>117145</t>
+          <t>116319</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>125151</t>
+          <t>124921</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,52%</t>
+          <t>90,88%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,6%</t>
         </is>
       </c>
     </row>
@@ -4155,57 +4155,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>68614</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>68614</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>68614</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>89</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>59378</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>59378</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>59378</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>68614</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>68614</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>68614</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4272,72 +4272,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>27067</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>18102</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>36570</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>5,54%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>3,7%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>7,48%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>34</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>23343</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>16590</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>31488</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>16354</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>32603</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>4,94%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>3,51%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>6,67%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>27067</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>18618</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>36711</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>5,54%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>38703</t>
+          <t>40027</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>62063</t>
+          <t>62323</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,49%</t>
         </is>
       </c>
     </row>
@@ -4385,72 +4385,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>658</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>461668</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>452165</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>470633</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>94,46%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>92,52%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>96,3%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>680</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>448947</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>440802</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>455700</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>439687</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>455936</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>95,06%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>93,33%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>96,49%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>658</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>461668</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>452024</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>470117</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>94,46%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,49%</t>
+          <t>93,1%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,19%</t>
+          <t>96,54%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>898962</t>
+          <t>898702</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>922322</t>
+          <t>920998</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,54%</t>
+          <t>93,51%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,97%</t>
+          <t>95,83%</t>
         </is>
       </c>
     </row>
@@ -4498,57 +4498,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>695</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>488735</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>488735</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>488735</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>714</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>472290</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>472290</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>472290</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>695</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>488735</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>488735</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>488735</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4615,72 +4615,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>5781</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2818</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>11335</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>3,08%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>1,5%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>6,05%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>8126</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>4156</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>14615</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>4263</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>14262</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>4,71%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>2,41%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>8,46%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>5781</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>2296</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>10890</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>3,08%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8430</t>
+          <t>8738</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>21275</t>
+          <t>21437</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,95%</t>
         </is>
       </c>
     </row>
@@ -4728,72 +4728,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>263</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>181714</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>176160</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>184677</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>96,92%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>93,95%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>98,5%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>247</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>164577</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>158088</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>168547</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>158441</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>168440</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>95,29%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>91,54%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>97,59%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>263</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>181714</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>176605</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>185199</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>96,92%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,19%</t>
+          <t>91,74%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>97,53%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>338922</t>
+          <t>338760</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>351767</t>
+          <t>351459</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,09%</t>
+          <t>94,05%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,57%</t>
         </is>
       </c>
     </row>
@@ -4841,57 +4841,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>271</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>187495</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>187495</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>187495</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>258</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>172703</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>172703</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>172703</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>271</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>187495</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>187495</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>187495</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4958,107 +4958,107 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>38600</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>29165</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>49869</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>5,18%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>3,92%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>6,7%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>46</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>32132</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>23611</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>41695</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>23158</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>42850</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>4,56%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>3,35%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>3,29%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>6,08%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>70732</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>58078</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>85840</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>4,88%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>4,01%</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
         <is>
           <t>5,92%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>38600</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>29652</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>50237</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>5,18%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>3,98%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>6,74%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>70732</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>57546</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>85532</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>4,88%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>3,97%</t>
-        </is>
-      </c>
-      <c r="W13" s="2" t="inlineStr">
-        <is>
-          <t>5,9%</t>
         </is>
       </c>
     </row>
@@ -5071,107 +5071,107 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>1012</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>706244</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>694975</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>715679</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>94,82%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>93,3%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>96,08%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>1015</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>672239</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>662676</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>680760</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>661521</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>681213</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>95,44%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>93,92%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>96,71%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>1378483</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>1363375</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>1391137</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>95,12%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>94,08%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>96,65%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>1012</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>706244</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>694607</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>715192</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>94,82%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>93,26%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>96,02%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>2027</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>1378483</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>1363683</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>1391669</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>95,12%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>94,1%</t>
-        </is>
-      </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>95,99%</t>
         </is>
       </c>
     </row>
@@ -5184,57 +5184,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>1065</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>1061</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>704371</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>1065</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5353,7 +5353,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -5364,7 +5364,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -5532,72 +5532,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>6478</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2789</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>12657</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>11,42%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>4,92%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>22,31%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>2163</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>625</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>6630</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>3,96%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>1,14%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>12,13%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>7022</t>
+          <t>2276</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3194</t>
+          <t>650</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13822</t>
+          <t>6376</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>22,29%</t>
+          <t>13,64%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5607,32 +5607,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>9186</t>
+          <t>8754</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4346</t>
+          <t>4328</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>17940</t>
+          <t>15593</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>15,07%</t>
         </is>
       </c>
     </row>
@@ -5645,72 +5645,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>50254</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>44075</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>53943</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>88,58%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>77,69%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>95,08%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>66</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>52515</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>48048</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>54053</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>96,04%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>87,87%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>98,86%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>54982</t>
+          <t>44482</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>48182</t>
+          <t>40382</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>58810</t>
+          <t>46108</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>88,67%</t>
+          <t>95,13%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>77,71%</t>
+          <t>86,36%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,85%</t>
+          <t>98,61%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>107496</t>
+          <t>94736</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>98742</t>
+          <t>87897</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>112336</t>
+          <t>99162</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>92,13%</t>
+          <t>91,54%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>84,62%</t>
+          <t>84,93%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>95,82%</t>
         </is>
       </c>
     </row>
@@ -5758,57 +5758,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>56732</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>56732</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>56732</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>69</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>54678</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>54678</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>54678</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>62004</t>
+          <t>46758</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>62004</t>
+          <t>46758</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>62004</t>
+          <t>46758</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5833,17 +5833,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>116682</t>
+          <t>103490</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>116682</t>
+          <t>103490</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>116682</t>
+          <t>103490</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5875,72 +5875,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>37292</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>27304</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>48383</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>7,87%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>5,76%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>10,2%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>39</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>26803</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>18336</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>36465</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>5,84%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>3,99%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>7,94%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>40450</t>
+          <t>27650</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>29414</t>
+          <t>20410</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>53353</t>
+          <t>38022</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5950,32 +5950,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>67252</t>
+          <t>64942</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>53745</t>
+          <t>53195</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>86320</t>
+          <t>81426</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>9,0%</t>
         </is>
       </c>
     </row>
@@ -5988,72 +5988,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>605</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>436837</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>425746</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>446825</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>92,13%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>89,8%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>94,24%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>602</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>432266</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>422604</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>440733</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>94,16%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>92,06%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>96,01%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>605</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>474375</t>
+          <t>403348</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>461472</t>
+          <t>392976</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>485411</t>
+          <t>410588</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>92,14%</t>
+          <t>93,58%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,64%</t>
+          <t>91,18%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,29%</t>
+          <t>95,26%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>906642</t>
+          <t>840185</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>887574</t>
+          <t>823701</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>920149</t>
+          <t>851932</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>93,09%</t>
+          <t>92,83%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,14%</t>
+          <t>91,0%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,48%</t>
+          <t>94,12%</t>
         </is>
       </c>
     </row>
@@ -6101,57 +6101,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>653</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>474129</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>474129</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>474129</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>641</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>459069</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>459069</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>459069</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>653</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>514825</t>
+          <t>430998</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>514825</t>
+          <t>430998</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>514825</t>
+          <t>430998</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>973894</t>
+          <t>905127</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>973894</t>
+          <t>905127</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>973894</t>
+          <t>905127</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6218,72 +6218,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>14708</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>9132</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>22774</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>8,73%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>5,42%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>13,52%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>7637</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>3775</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>12765</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>5,14%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>2,54%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>8,58%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>15163</t>
+          <t>8194</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9175</t>
+          <t>4195</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>24403</t>
+          <t>14171</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6293,32 +6293,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>22800</t>
+          <t>22902</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>15420</t>
+          <t>15381</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>32828</t>
+          <t>33631</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>10,59%</t>
         </is>
       </c>
     </row>
@@ -6331,72 +6331,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>153711</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>145645</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>159287</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>91,27%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>86,48%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>94,58%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>218</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>141083</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>135955</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>144945</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>94,86%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>91,42%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>97,46%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>220</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>168186</t>
+          <t>140912</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>158946</t>
+          <t>134935</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>174174</t>
+          <t>144911</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>91,73%</t>
+          <t>94,5%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>86,69%</t>
+          <t>90,5%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,0%</t>
+          <t>97,19%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6406,32 +6406,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>309269</t>
+          <t>294623</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>299241</t>
+          <t>283894</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>316649</t>
+          <t>302144</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>93,13%</t>
+          <t>92,79%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,11%</t>
+          <t>89,41%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,36%</t>
+          <t>95,16%</t>
         </is>
       </c>
     </row>
@@ -6444,57 +6444,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>168419</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>168419</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>168419</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>229</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>148720</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>148720</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>148720</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>238</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>183349</t>
+          <t>149106</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>183349</t>
+          <t>149106</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>183349</t>
+          <t>149106</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6519,17 +6519,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>332069</t>
+          <t>317525</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>332069</t>
+          <t>317525</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>332069</t>
+          <t>317525</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6561,72 +6561,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>58479</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>45376</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>72397</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>8,36%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>6,49%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>10,35%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>36603</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>27402</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>50210</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>5,53%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>4,14%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>7,58%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>62635</t>
+          <t>38120</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>49293</t>
+          <t>28734</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>79927</t>
+          <t>49207</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6636,32 +6636,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>99238</t>
+          <t>96599</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>80718</t>
+          <t>81305</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>118415</t>
+          <t>116227</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,76%</t>
         </is>
       </c>
     </row>
@@ -6674,72 +6674,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>900</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>640801</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>626883</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>653904</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>91,64%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>89,65%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>93,51%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>886</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>625864</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>612257</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>635065</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>94,47%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>92,42%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>95,86%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>900</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>697542</t>
+          <t>588742</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>680250</t>
+          <t>577655</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>710884</t>
+          <t>598128</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>91,76%</t>
+          <t>93,92%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,49%</t>
+          <t>92,15%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,52%</t>
+          <t>95,42%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6749,32 +6749,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1323407</t>
+          <t>1229543</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1304230</t>
+          <t>1209915</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1341927</t>
+          <t>1244837</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>93,02%</t>
+          <t>92,72%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,68%</t>
+          <t>91,24%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,33%</t>
+          <t>93,87%</t>
         </is>
       </c>
     </row>
@@ -6787,57 +6787,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>974</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>699280</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>699280</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>699280</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>939</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>662467</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>662467</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>662467</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>974</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>760177</t>
+          <t>626862</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>760177</t>
+          <t>626862</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>760177</t>
+          <t>626862</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6862,17 +6862,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1422645</t>
+          <t>1326142</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1422645</t>
+          <t>1326142</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1422645</t>
+          <t>1326142</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
